--- a/test_data/examples/smeaheia/smeaheia_workbook.xlsx
+++ b/test_data/examples/smeaheia/smeaheia_workbook.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Header" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GridPolicy" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HoleCasings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Plugs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Stratigraphy" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SubsurfaceAssumptions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Survey" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HoleCasings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Plugs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stratigraphy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SubsurfaceAssumptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -722,306 +723,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>md_rkb</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>inclination_deg</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>top_rkb</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bottom_rkb</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>diameter_in</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>shoe</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>hc_perm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hole 36 in</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>hole</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>395</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hole 17 1/2 in</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>hole</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>395</v>
-      </c>
-      <c r="D3" t="n">
-        <v>720</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>17 1/2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hole 12 1/4 in</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>hole</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>720</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1185</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12 1/4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hole 8 1/2 in</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>hole</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3186</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8 1/2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Casing 30 in</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>casing</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>394</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cement 30 in</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>casing cement</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>394</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Casing 13 3/8 in</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>casing</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>709</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>13 3/8</t>
-        </is>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cement 13 3/8 in</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>casing cement</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>709</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>13 3/8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Casing 9 5/8 in</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>casing</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>622</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1137.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9 5/8</t>
-        </is>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cement 9 5/8 in</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>casing cement</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>706</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1137.5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>9 5/8</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>5</v>
+          <t>azimuth_deg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,50 +780,280 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cement_perm</t>
+          <t>diameter_in</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>shoe</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hc_perm</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cplug9</t>
+          <t>Hole 36 in</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cement</t>
+          <t>hole</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>375</v>
+        <v>335.5</v>
       </c>
       <c r="D2" t="n">
-        <v>583</v>
+        <v>395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mplug2</t>
+          <t>Hole 17 1/2 in</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mechanical plug</t>
+          <t>hole</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1049</v>
+        <v>395</v>
       </c>
       <c r="D3" t="n">
-        <v>1069</v>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
+        <v>720</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>17 1/2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hole 12 1/4 in</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hole</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>720</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12 1/4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hole 8 1/2 in</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hole</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3186</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8 1/2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Casing 30 in</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>casing</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>394</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cement 30 in</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>casing cement</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>394</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Casing 13 3/8 in</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>casing</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>709</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13 3/8</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cement 13 3/8 in</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>casing cement</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>709</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13 3/8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Casing 9 5/8 in</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>casing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>622</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1137.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9 5/8</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cement 9 5/8 in</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>casing cement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>706</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1137.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9 5/8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,324 +1078,65 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>top_rkb</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>bottom_rkb</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unit_type</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cement_perm</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NORDLAND GP</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>336</v>
+          <t>cplug9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>535</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
+        <v>375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ROGALAND GP</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>535</v>
+          <t>mplug2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mechanical plug</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>846</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SHETLAND GP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>846</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1081</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CROMER KNOLL GP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1081</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1109</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DRAUPNE FM</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1109</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1216</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HEATHER FM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1216</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1238</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SOGNEFJORD FM</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1238</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1306</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>reservoir</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HEATHER FM</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1306</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1366</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FENSFJORD FM</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1366</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1595</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>reservoir</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HEATHER FM</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1595</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1598</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KROSSFJORD FM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1598</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1645</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>reservoir</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HEATHER FM</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1645</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BRENT GP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1783</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DUNLIN GP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1783</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1816</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STATFJORD GP</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1816</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1832</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HEGRE GP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1832</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3132</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BASEMENT</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3132</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3186</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>undefined</t>
-        </is>
+        <v>1049</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1069</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1460,69 +1150,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>temperature_gradient</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ground_temperature</t>
+          <t>top_rkb</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fluid_type</t>
+          <t>bottom_rkb</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>z_fluid_contact</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>p_fluid_contact</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>z_resrv</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>p_resrv</t>
+          <t>unit_type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>31</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NORDLAND GP</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>co2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>150</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1550</v>
-      </c>
-      <c r="G2" t="n">
-        <v>155</v>
+        <v>336</v>
+      </c>
+      <c r="C2" t="n">
+        <v>535</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ROGALAND GP</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>535</v>
+      </c>
+      <c r="C3" t="n">
+        <v>846</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SHETLAND GP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>846</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CROMER KNOLL GP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DRAUPNE FM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HEATHER FM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1216</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SOGNEFJORD FM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1238</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1306</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HEATHER FM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1306</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FENSFJORD FM</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1366</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1595</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HEATHER FM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1595</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1598</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KROSSFJORD FM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1598</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HEATHER FM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1645</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BRENT GP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DUNLIN GP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STATFJORD GP</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HEGRE GP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3132</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BASEMENT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3132</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3186</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1536,12 +1492,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>temperature_gradient</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ground_temperature</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fluid_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>z_fluid_contact</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p_fluid_contact</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>z_resrv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>p_resrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>co2</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G2" t="n">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1556,12 +1588,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GridPolicy and SubsurfaceAssumptions are editable example scenario values and must be reviewed for a real case.</t>
+          <t>Survey is optional: leave it empty for vertical wells or add md_rkb, inclination_deg, and azimuth_deg rows for deviation.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
+        <is>
+          <t>GridPolicy and SubsurfaceAssumptions are editable example scenario values and must be reviewed for a real case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>z_fluid_contact and p_fluid_contact define the GAS_WATER datum and WGC depth in CIRRUS.</t>
         </is>

--- a/test_data/examples/smeaheia/smeaheia_workbook.xlsx
+++ b/test_data/examples/smeaheia/smeaheia_workbook.xlsx
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1500</v>
+        <v>1282.5</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>129.99</v>
       </c>
       <c r="F2" t="n">
-        <v>1550</v>
+        <v>1282.5</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>129.99</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/examples/smeaheia/smeaheia_workbook.xlsx
+++ b/test_data/examples/smeaheia/smeaheia_workbook.xlsx
@@ -1492,69 +1492,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>case_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>temperature_gradient</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ground_temperature</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fluid_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>z_fluid_contact</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>p_fluid_contact</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>z_resrv</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p_resrv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>31</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>co2</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1282.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>129.99</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1282.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>129.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>co2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F3" t="n">
+        <v>131</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H3" t="n">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1568,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +1646,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Multiple rows in SubsurfaceAssumptions define a design matrix of scenarios that can be run with --case-name selection.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
